--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -1162,7 +1162,7 @@
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.5278,0.5193,0.0339,0.0021</t>
+    <t>0.5278,0.5192,0.0339,0.0021</t>
   </si>
   <si>
     <t>0.1588,0.0370,0.7971,0.0094</t>
@@ -1387,7 +1387,7 @@
     <t>0.0205,0.0015,0.9832,0.0008</t>
   </si>
   <si>
-    <t>0.1200,0.0062,0.8749,0.0025</t>
+    <t>0.1200,0.0062,0.8750,0.0025</t>
   </si>
   <si>
     <t>0.1835,0.0003,0.8875,0.0003</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
   <si>
     <t>Filename</t>
   </si>
@@ -817,6 +817,9 @@
     <t>0,0,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,0</t>
   </si>
   <si>
@@ -826,16 +829,22 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8986,0.0034,0.0326,0.0133</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.8983,0.0034,0.0328,0.0133</t>
   </si>
   <si>
     <t>0.0055,0.0019,0.0005,0.9986</t>
   </si>
   <si>
-    <t>0.9267,0.0016,0.0007,0.0314</t>
-  </si>
-  <si>
-    <t>0.1331,0.0012,0.0023,0.9289</t>
+    <t>0.9265,0.0016,0.0007,0.0314</t>
+  </si>
+  <si>
+    <t>0.1330,0.0012,0.0023,0.9289</t>
   </si>
   <si>
     <t>0.9934,0.0021,0.0015,0.0002</t>
@@ -844,16 +853,16 @@
     <t>0.9897,0.0090,0.0013,0.0004</t>
   </si>
   <si>
-    <t>0.9888,0.0034,0.0030,0.0002</t>
+    <t>0.9888,0.0034,0.0031,0.0002</t>
   </si>
   <si>
     <t>0.9941,0.0019,0.0012,0.0001</t>
   </si>
   <si>
-    <t>0.9307,0.0881,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9847,0.0150,0.0018,0.0007</t>
+    <t>0.9306,0.0881,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9846,0.0150,0.0018,0.0007</t>
   </si>
   <si>
     <t>0.9949,0.0020,0.0009,0.0001</t>
@@ -862,19 +871,19 @@
     <t>0.9925,0.0030,0.0016,0.0002</t>
   </si>
   <si>
-    <t>0.6226,0.0075,0.3643,0.0042</t>
-  </si>
-  <si>
-    <t>0.0180,0.0178,0.9736,0.0025</t>
-  </si>
-  <si>
-    <t>0.2429,0.0008,0.8523,0.0002</t>
-  </si>
-  <si>
-    <t>0.0487,0.0035,0.9585,0.0020</t>
-  </si>
-  <si>
-    <t>0.5022,0.0007,0.6055,0.0003</t>
+    <t>0.6220,0.0075,0.3650,0.0042</t>
+  </si>
+  <si>
+    <t>0.0179,0.0177,0.9736,0.0025</t>
+  </si>
+  <si>
+    <t>0.2427,0.0007,0.8525,0.0002</t>
+  </si>
+  <si>
+    <t>0.0487,0.0035,0.9586,0.0020</t>
+  </si>
+  <si>
+    <t>0.5018,0.0007,0.6059,0.0003</t>
   </si>
   <si>
     <t>0.0007,0.9991,0.0037,0.0006</t>
@@ -892,16 +901,16 @@
     <t>0.0007,0.9994,0.0048,0.0001</t>
   </si>
   <si>
-    <t>0.2514,0.0012,0.7864,0.0022</t>
-  </si>
-  <si>
-    <t>0.0524,0.0132,0.9272,0.0067</t>
+    <t>0.2510,0.0012,0.7868,0.0022</t>
+  </si>
+  <si>
+    <t>0.0523,0.0132,0.9273,0.0067</t>
   </si>
   <si>
     <t>0.0165,0.0003,0.9905,0.0003</t>
   </si>
   <si>
-    <t>0.0191,0.0017,0.9845,0.0013</t>
+    <t>0.0190,0.0017,0.9846,0.0013</t>
   </si>
   <si>
     <t>0.0135,0.0008,0.9909,0.0009</t>
@@ -913,52 +922,52 @@
     <t>0.0069,0.0001,0.9959,0.0003</t>
   </si>
   <si>
-    <t>0.5164,0.4452,0.0364,0.0026</t>
-  </si>
-  <si>
-    <t>0.9203,0.0956,0.0030,0.0011</t>
+    <t>0.5160,0.4455,0.0364,0.0026</t>
+  </si>
+  <si>
+    <t>0.9203,0.0955,0.0030,0.0011</t>
   </si>
   <si>
     <t>0.0020,0.0006,0.9987,0.0004</t>
   </si>
   <si>
-    <t>0.0191,0.1292,0.8686,0.0011</t>
-  </si>
-  <si>
-    <t>0.9501,0.0087,0.0187,0.0010</t>
+    <t>0.0191,0.1288,0.8689,0.0011</t>
+  </si>
+  <si>
+    <t>0.9500,0.0087,0.0187,0.0010</t>
   </si>
   <si>
     <t>0.9232,0.0327,0.0235,0.0008</t>
   </si>
   <si>
-    <t>0.2541,0.8220,0.0191,0.0021</t>
-  </si>
-  <si>
-    <t>0.0053,0.9534,0.5661,0.0013</t>
-  </si>
-  <si>
-    <t>0.0004,0.6161,0.9891,0.0001</t>
+    <t>0.2539,0.8223,0.0191,0.0021</t>
+  </si>
+  <si>
+    <t>0.0053,0.9534,0.5662,0.0013</t>
+  </si>
+  <si>
+    <t>0.0004,0.6155,0.9891,0.0001</t>
   </si>
   <si>
     <t>0.0034,0.0013,0.9964,0.0005</t>
   </si>
   <si>
-    <t>0.0389,0.0188,0.9375,0.0028</t>
-  </si>
-  <si>
-    <t>0.0450,0.0014,0.9570,0.0075</t>
-  </si>
-  <si>
-    <t>0.0009,0.3585,0.9821,0.0004</t>
+    <t>0.0389,0.0188,0.9376,0.0028</t>
+  </si>
+  <si>
+    <t>0.0449,0.0014,0.9571,0.0075</t>
+  </si>
+  <si>
+    <t>0.0009,0.3578,0.9821,0.0004</t>
   </si>
   <si>
     <t>0.0039,0.9949,0.0079,0.0002</t>
   </si>
   <si>
-    <t>0.0055,0.0063,0.9911,0.0009</t>
-  </si>
-  <si>
-    <t>0.0009,0.9226,0.0008,0.7889</t>
+    <t>0.0055,0.0062,0.9911,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.9227,0.0008,0.7889</t>
   </si>
   <si>
     <t>0.0001,1.0000,0.0001,0.0000</t>
@@ -973,7 +982,7 @@
     <t>0.0002,0.0064,0.9992,0.0001</t>
   </si>
   <si>
-    <t>0.0012,0.2325,0.9834,0.0014</t>
+    <t>0.0012,0.2323,0.9834,0.0014</t>
   </si>
   <si>
     <t>0.0069,0.0010,0.9932,0.0012</t>
@@ -988,16 +997,16 @@
     <t>0.0172,0.0179,0.9603,0.0042</t>
   </si>
   <si>
-    <t>0.9628,0.0199,0.0115,0.0008</t>
+    <t>0.9627,0.0199,0.0116,0.0008</t>
   </si>
   <si>
     <t>0.9755,0.0016,0.0144,0.0002</t>
   </si>
   <si>
-    <t>0.9671,0.0163,0.0089,0.0040</t>
-  </si>
-  <si>
-    <t>0.2055,0.0018,0.8405,0.0007</t>
+    <t>0.9670,0.0163,0.0089,0.0040</t>
+  </si>
+  <si>
+    <t>0.2050,0.0018,0.8411,0.0007</t>
   </si>
   <si>
     <t>0.9855,0.0012,0.0064,0.0002</t>
@@ -1009,16 +1018,16 @@
     <t>0.9893,0.0023,0.0035,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9972,0.7952,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0191,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.0081,0.9952,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.9857,0.8255,0.0004</t>
+    <t>0.0001,0.9972,0.7956,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0190,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0080,0.9952,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.9857,0.8260,0.0004</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9999,0.0001</t>
@@ -1030,25 +1039,25 @@
     <t>0.0003,0.9997,0.0012,0.0000</t>
   </si>
   <si>
-    <t>0.9315,0.0008,0.0582,0.0002</t>
-  </si>
-  <si>
-    <t>0.1152,0.0780,0.8291,0.0045</t>
+    <t>0.9314,0.0008,0.0583,0.0002</t>
+  </si>
+  <si>
+    <t>0.1152,0.0779,0.8293,0.0045</t>
   </si>
   <si>
     <t>0.0198,0.0075,0.9840,0.0017</t>
   </si>
   <si>
-    <t>0.0008,0.9656,0.8563,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.8326,0.9723,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0706,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9339,0.9469,0.0005</t>
+    <t>0.0008,0.9655,0.8566,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.8320,0.9724,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0707,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9338,0.9469,0.0005</t>
   </si>
   <si>
     <t>0.0029,0.0025,0.0045,0.9986</t>
@@ -1060,7 +1069,7 @@
     <t>0.0017,0.0001,0.0003,0.9997</t>
   </si>
   <si>
-    <t>0.0026,0.0004,0.0037,0.9988</t>
+    <t>0.0025,0.0004,0.0037,0.9988</t>
   </si>
   <si>
     <t>0.0085,0.0041,0.0038,0.9961</t>
@@ -1069,25 +1078,25 @@
     <t>0.0002,0.0012,0.0035,0.9997</t>
   </si>
   <si>
-    <t>0.0002,0.9960,0.7731,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.6758,0.9851,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.9742,0.3959,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.7251,0.9841,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9932,0.9111,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9970,0.1883,0.0003</t>
-  </si>
-  <si>
-    <t>0.9891,0.0138,0.0006,0.0003</t>
+    <t>0.0002,0.9960,0.7734,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.6753,0.9851,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.9742,0.3966,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.7245,0.9842,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9932,0.9113,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9970,0.1887,0.0003</t>
+  </si>
+  <si>
+    <t>0.9891,0.0139,0.0006,0.0003</t>
   </si>
   <si>
     <t>0.9670,0.0334,0.0036,0.0006</t>
@@ -1096,7 +1105,7 @@
     <t>0.9491,0.0756,0.0018,0.0004</t>
   </si>
   <si>
-    <t>0.9854,0.0208,0.0006,0.0003</t>
+    <t>0.9854,0.0209,0.0006,0.0003</t>
   </si>
   <si>
     <t>0.9918,0.0054,0.0012,0.0001</t>
@@ -1108,10 +1117,10 @@
     <t>0.9825,0.0044,0.0056,0.0006</t>
   </si>
   <si>
-    <t>0.9468,0.0061,0.0105,0.0020</t>
-  </si>
-  <si>
-    <t>0.9911,0.0019,0.0024,0.0004</t>
+    <t>0.9465,0.0061,0.0106,0.0020</t>
+  </si>
+  <si>
+    <t>0.9910,0.0019,0.0024,0.0004</t>
   </si>
   <si>
     <t>0.9868,0.0111,0.0023,0.0010</t>
@@ -1123,10 +1132,10 @@
     <t>0.9930,0.0042,0.0011,0.0006</t>
   </si>
   <si>
-    <t>0.9858,0.0114,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.9930,0.0035,0.0013,0.0011</t>
+    <t>0.9858,0.0115,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9929,0.0035,0.0013,0.0011</t>
   </si>
   <si>
     <t>0.9946,0.0040,0.0006,0.0004</t>
@@ -1141,19 +1150,19 @@
     <t>0.0227,0.0031,0.9803,0.0017</t>
   </si>
   <si>
-    <t>0.9362,0.0001,0.0887,0.0002</t>
-  </si>
-  <si>
-    <t>0.0446,0.0030,0.9550,0.0013</t>
+    <t>0.9361,0.0001,0.0888,0.0002</t>
+  </si>
+  <si>
+    <t>0.0445,0.0030,0.9550,0.0013</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.2571,0.8096,0.0027,0.0010</t>
-  </si>
-  <si>
-    <t>0.0507,0.9592,0.0241,0.0047</t>
+    <t>0.2570,0.8097,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.0506,0.9593,0.0241,0.0047</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0002,0.0000</t>
@@ -1162,22 +1171,22 @@
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.5278,0.5192,0.0339,0.0021</t>
-  </si>
-  <si>
-    <t>0.1588,0.0370,0.7971,0.0094</t>
-  </si>
-  <si>
-    <t>0.0430,0.0087,0.9497,0.0051</t>
-  </si>
-  <si>
-    <t>0.2357,0.0090,0.7459,0.0032</t>
-  </si>
-  <si>
-    <t>0.1024,0.0184,0.8887,0.0099</t>
-  </si>
-  <si>
-    <t>0.0003,0.5634,0.5832,0.2306</t>
+    <t>0.5273,0.5198,0.0339,0.0021</t>
+  </si>
+  <si>
+    <t>0.1587,0.0370,0.7974,0.0094</t>
+  </si>
+  <si>
+    <t>0.0430,0.0086,0.9498,0.0050</t>
+  </si>
+  <si>
+    <t>0.2355,0.0090,0.7462,0.0032</t>
+  </si>
+  <si>
+    <t>0.1023,0.0184,0.8888,0.0099</t>
+  </si>
+  <si>
+    <t>0.0003,0.5629,0.5835,0.2306</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0009,0.0000</t>
@@ -1189,22 +1198,22 @@
     <t>0.0001,0.9996,0.0003,0.0020</t>
   </si>
   <si>
-    <t>0.0002,0.9993,0.0286,0.0002</t>
+    <t>0.0002,0.9993,0.0287,0.0002</t>
   </si>
   <si>
     <t>0.0025,0.9921,0.1937,0.0009</t>
   </si>
   <si>
-    <t>0.1906,0.8044,0.0647,0.0030</t>
-  </si>
-  <si>
-    <t>0.1532,0.7874,0.1262,0.0107</t>
-  </si>
-  <si>
-    <t>0.9810,0.0021,0.0052,0.0009</t>
-  </si>
-  <si>
-    <t>0.9873,0.0079,0.0006,0.0011</t>
+    <t>0.1905,0.8046,0.0647,0.0030</t>
+  </si>
+  <si>
+    <t>0.1531,0.7876,0.1261,0.0107</t>
+  </si>
+  <si>
+    <t>0.9810,0.0021,0.0053,0.0009</t>
+  </si>
+  <si>
+    <t>0.9872,0.0079,0.0006,0.0011</t>
   </si>
   <si>
     <t>0.9879,0.0080,0.0018,0.0010</t>
@@ -1213,40 +1222,40 @@
     <t>0.9874,0.0026,0.0040,0.0007</t>
   </si>
   <si>
-    <t>0.9840,0.0057,0.0035,0.0029</t>
-  </si>
-  <si>
-    <t>0.9716,0.0022,0.0103,0.0006</t>
-  </si>
-  <si>
-    <t>0.9935,0.0021,0.0014,0.0003</t>
+    <t>0.9839,0.0057,0.0035,0.0029</t>
+  </si>
+  <si>
+    <t>0.9715,0.0022,0.0104,0.0006</t>
+  </si>
+  <si>
+    <t>0.9934,0.0021,0.0014,0.0003</t>
   </si>
   <si>
     <t>0.9938,0.0013,0.0016,0.0002</t>
   </si>
   <si>
-    <t>0.0010,0.7650,0.9645,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.4789,0.9905,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0220,0.9976,0.0002</t>
+    <t>0.0010,0.7650,0.9646,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.4776,0.9905,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0219,0.9976,0.0002</t>
   </si>
   <si>
     <t>0.0085,0.0052,0.9922,0.0003</t>
   </si>
   <si>
-    <t>0.9084,0.0015,0.0645,0.0015</t>
-  </si>
-  <si>
-    <t>0.1992,0.6612,0.0507,0.0066</t>
-  </si>
-  <si>
-    <t>0.1227,0.0002,0.9262,0.0011</t>
-  </si>
-  <si>
-    <t>0.3812,0.0089,0.5844,0.0062</t>
+    <t>0.9083,0.0015,0.0646,0.0015</t>
+  </si>
+  <si>
+    <t>0.1992,0.6613,0.0507,0.0066</t>
+  </si>
+  <si>
+    <t>0.1224,0.0002,0.9264,0.0011</t>
+  </si>
+  <si>
+    <t>0.3810,0.0089,0.5847,0.0062</t>
   </si>
   <si>
     <t>0.0171,0.0001,0.0021,0.9945</t>
@@ -1261,7 +1270,7 @@
     <t>0.0039,0.0005,0.0024,0.9990</t>
   </si>
   <si>
-    <t>0.0002,0.9944,0.7318,0.0002</t>
+    <t>0.0002,0.9944,0.7323,0.0002</t>
   </si>
   <si>
     <t>0.9850,0.0024,0.0049,0.0004</t>
@@ -1288,19 +1297,19 @@
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8180,0.0000,0.0953,0.0011</t>
-  </si>
-  <si>
-    <t>0.9855,0.0050,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.6136,0.2490,0.0446,0.0013</t>
+    <t>0.8176,0.0000,0.0956,0.0011</t>
+  </si>
+  <si>
+    <t>0.9854,0.0050,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.6134,0.2490,0.0448,0.0013</t>
   </si>
   <si>
     <t>0.9813,0.0039,0.0063,0.0005</t>
   </si>
   <si>
-    <t>0.9261,0.0445,0.0190,0.0015</t>
+    <t>0.9260,0.0445,0.0190,0.0015</t>
   </si>
   <si>
     <t>0.0310,0.9682,0.0143,0.0061</t>
@@ -1309,19 +1318,19 @@
     <t>0.8338,0.0942,0.0655,0.0029</t>
   </si>
   <si>
-    <t>0.6479,0.0223,0.2595,0.0029</t>
+    <t>0.6472,0.0222,0.2601,0.0029</t>
   </si>
   <si>
     <t>0.9887,0.0093,0.0015,0.0004</t>
   </si>
   <si>
-    <t>0.9881,0.0106,0.0010,0.0008</t>
+    <t>0.9881,0.0107,0.0010,0.0008</t>
   </si>
   <si>
     <t>0.9800,0.0048,0.0072,0.0008</t>
   </si>
   <si>
-    <t>0.9904,0.0017,0.0027,0.0002</t>
+    <t>0.9904,0.0017,0.0028,0.0002</t>
   </si>
   <si>
     <t>0.9885,0.0046,0.0025,0.0003</t>
@@ -1336,61 +1345,61 @@
     <t>0.9925,0.0025,0.0015,0.0002</t>
   </si>
   <si>
-    <t>0.6143,0.4109,0.0120,0.0056</t>
-  </si>
-  <si>
-    <t>0.1389,0.8995,0.0115,0.0033</t>
-  </si>
-  <si>
-    <t>0.6896,0.4101,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9137,0.0187,0.0483,0.0012</t>
+    <t>0.6141,0.4113,0.0120,0.0056</t>
+  </si>
+  <si>
+    <t>0.1388,0.8996,0.0115,0.0033</t>
+  </si>
+  <si>
+    <t>0.6891,0.4107,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9134,0.0187,0.0486,0.0012</t>
   </si>
   <si>
     <t>0.9884,0.0080,0.0021,0.0002</t>
   </si>
   <si>
-    <t>0.8663,0.0476,0.0607,0.0019</t>
+    <t>0.8661,0.0476,0.0609,0.0019</t>
   </si>
   <si>
     <t>0.9862,0.0027,0.0050,0.0003</t>
   </si>
   <si>
-    <t>0.8824,0.1188,0.0205,0.0032</t>
+    <t>0.8822,0.1190,0.0206,0.0032</t>
   </si>
   <si>
     <t>0.0091,0.0051,0.9952,0.0004</t>
   </si>
   <si>
-    <t>0.8355,0.0949,0.0523,0.0014</t>
-  </si>
-  <si>
-    <t>0.0012,0.0004,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.1095,0.9956,0.0007</t>
+    <t>0.8352,0.0950,0.0525,0.0014</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.1091,0.9956,0.0007</t>
   </si>
   <si>
     <t>0.0092,0.0021,0.9932,0.0013</t>
   </si>
   <si>
-    <t>0.0024,0.1136,0.9846,0.0006</t>
+    <t>0.0024,0.1131,0.9846,0.0006</t>
   </si>
   <si>
     <t>0.0011,0.0009,0.9990,0.0001</t>
   </si>
   <si>
-    <t>0.0016,0.0001,0.9990,0.0000</t>
+    <t>0.0016,0.0001,0.9991,0.0000</t>
   </si>
   <si>
     <t>0.0205,0.0015,0.9832,0.0008</t>
   </si>
   <si>
-    <t>0.1200,0.0062,0.8750,0.0025</t>
-  </si>
-  <si>
-    <t>0.1835,0.0003,0.8875,0.0003</t>
+    <t>0.1198,0.0062,0.8751,0.0025</t>
+  </si>
+  <si>
+    <t>0.1832,0.0003,0.8877,0.0003</t>
   </si>
   <si>
     <t>0.4078,0.0426,0.4620,0.0067</t>
@@ -1402,13 +1411,13 @@
     <t>0.0171,0.0282,0.9585,0.0009</t>
   </si>
   <si>
-    <t>0.0650,0.0024,0.9494,0.0012</t>
-  </si>
-  <si>
-    <t>0.0853,0.0060,0.9182,0.0045</t>
-  </si>
-  <si>
-    <t>0.4317,0.0347,0.4612,0.0049</t>
+    <t>0.0649,0.0024,0.9495,0.0012</t>
+  </si>
+  <si>
+    <t>0.0852,0.0060,0.9183,0.0045</t>
+  </si>
+  <si>
+    <t>0.4316,0.0346,0.4615,0.0049</t>
   </si>
   <si>
     <t>0.0559,0.9716,0.0078,0.0003</t>
@@ -1417,37 +1426,37 @@
     <t>0.0054,0.9974,0.0010,0.0001</t>
   </si>
   <si>
-    <t>0.1058,0.9471,0.0026,0.0004</t>
+    <t>0.1057,0.9472,0.0026,0.0004</t>
   </si>
   <si>
     <t>0.9741,0.0243,0.0033,0.0002</t>
   </si>
   <si>
-    <t>0.6353,0.5080,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.0901,0.9168,0.0134,0.0017</t>
-  </si>
-  <si>
-    <t>0.9319,0.0032,0.0368,0.0011</t>
-  </si>
-  <si>
-    <t>0.1916,0.0263,0.7644,0.0201</t>
-  </si>
-  <si>
-    <t>0.1353,0.0016,0.8665,0.0098</t>
-  </si>
-  <si>
-    <t>0.5087,0.0219,0.3714,0.0041</t>
+    <t>0.6350,0.5084,0.0039,0.0004</t>
+  </si>
+  <si>
+    <t>0.0902,0.9166,0.0134,0.0017</t>
+  </si>
+  <si>
+    <t>0.9318,0.0032,0.0369,0.0011</t>
+  </si>
+  <si>
+    <t>0.1914,0.0263,0.7648,0.0201</t>
+  </si>
+  <si>
+    <t>0.1350,0.0016,0.8668,0.0098</t>
+  </si>
+  <si>
+    <t>0.5087,0.0219,0.3715,0.0041</t>
   </si>
   <si>
     <t>0.0072,0.0005,0.9947,0.0005</t>
   </si>
   <si>
-    <t>0.0475,0.0058,0.9646,0.0017</t>
-  </si>
-  <si>
-    <t>0.0312,0.0419,0.9351,0.0010</t>
+    <t>0.0474,0.0058,0.9647,0.0017</t>
+  </si>
+  <si>
+    <t>0.0312,0.0419,0.9352,0.0010</t>
   </si>
   <si>
     <t>0.0070,0.0019,0.9935,0.0003</t>
@@ -1462,13 +1471,13 @@
     <t>0.9654,0.0253,0.0071,0.0011</t>
   </si>
   <si>
-    <t>0.8694,0.1279,0.0059,0.0030</t>
-  </si>
-  <si>
-    <t>0.9807,0.0226,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.9427,0.0539,0.0099,0.0022</t>
+    <t>0.8692,0.1282,0.0059,0.0030</t>
+  </si>
+  <si>
+    <t>0.9807,0.0227,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9426,0.0540,0.0099,0.0022</t>
   </si>
   <si>
     <t>0.9621,0.0416,0.0035,0.0009</t>
@@ -1483,10 +1492,10 @@
     <t>0.0155,0.0025,0.9905,0.0010</t>
   </si>
   <si>
-    <t>0.1213,0.0514,0.8355,0.0023</t>
-  </si>
-  <si>
-    <t>0.3809,0.0106,0.6190,0.0083</t>
+    <t>0.1212,0.0513,0.8356,0.0023</t>
+  </si>
+  <si>
+    <t>0.3801,0.0106,0.6200,0.0083</t>
   </si>
   <si>
     <t>0.0008,0.0002,0.9993,0.0001</t>
@@ -1495,7 +1504,7 @@
     <t>0.0002,0.0013,0.9994,0.0002</t>
   </si>
   <si>
-    <t>0.0072,0.0465,0.9684,0.0018</t>
+    <t>0.0072,0.0464,0.9684,0.0018</t>
   </si>
   <si>
     <t>0.0384,0.0117,0.9528,0.0016</t>
@@ -1507,25 +1516,25 @@
     <t>0.0456,0.0206,0.9334,0.0057</t>
   </si>
   <si>
-    <t>0.6852,0.0010,0.3330,0.0020</t>
-  </si>
-  <si>
-    <t>0.2253,0.0009,0.7685,0.0067</t>
-  </si>
-  <si>
-    <t>0.9440,0.0139,0.0223,0.0011</t>
+    <t>0.6850,0.0010,0.3332,0.0020</t>
+  </si>
+  <si>
+    <t>0.2251,0.0009,0.7688,0.0067</t>
+  </si>
+  <si>
+    <t>0.9439,0.0139,0.0224,0.0011</t>
   </si>
   <si>
     <t>0.9924,0.0056,0.0009,0.0001</t>
   </si>
   <si>
-    <t>0.9680,0.0402,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.9892,0.0077,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.8837,0.1205,0.0058,0.0008</t>
+    <t>0.9680,0.0403,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9892,0.0078,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.8836,0.1207,0.0058,0.0008</t>
   </si>
   <si>
     <t>0.9914,0.0025,0.0018,0.0002</t>
@@ -1537,10 +1546,10 @@
     <t>0.9830,0.0201,0.0018,0.0007</t>
   </si>
   <si>
-    <t>0.9851,0.0075,0.0028,0.0007</t>
-  </si>
-  <si>
-    <t>0.0092,0.0322,0.9791,0.0012</t>
+    <t>0.9850,0.0075,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.0092,0.0321,0.9791,0.0012</t>
   </si>
   <si>
     <t>0.0015,0.0030,0.9984,0.0001</t>
@@ -1549,22 +1558,22 @@
     <t>0.0022,0.0031,0.9974,0.0002</t>
   </si>
   <si>
-    <t>0.0374,0.0488,0.8801,0.0021</t>
-  </si>
-  <si>
-    <t>0.0199,0.0007,0.9871,0.0004</t>
-  </si>
-  <si>
-    <t>0.6912,0.0457,0.0650,0.0196</t>
-  </si>
-  <si>
-    <t>0.1117,0.0256,0.8086,0.0080</t>
+    <t>0.0374,0.0488,0.8802,0.0021</t>
+  </si>
+  <si>
+    <t>0.0199,0.0007,0.9872,0.0004</t>
+  </si>
+  <si>
+    <t>0.6909,0.0457,0.0652,0.0196</t>
+  </si>
+  <si>
+    <t>0.1117,0.0256,0.8088,0.0080</t>
   </si>
   <si>
     <t>0.0037,0.0005,0.9970,0.0006</t>
   </si>
   <si>
-    <t>0.8851,0.0004,0.0115,0.0242</t>
+    <t>0.8848,0.0004,0.0115,0.0242</t>
   </si>
   <si>
     <t>0.0008,0.0050,0.0004,0.9997</t>
@@ -1573,13 +1582,13 @@
     <t>0.0025,0.0008,0.0121,0.9982</t>
   </si>
   <si>
-    <t>0.0001,0.0002,0.0643,0.9997</t>
+    <t>0.0001,0.0002,0.0645,0.9997</t>
   </si>
   <si>
     <t>0.0001,0.0009,0.0027,0.9999</t>
   </si>
   <si>
-    <t>0.7006,0.0051,0.0297,0.2107</t>
+    <t>0.7004,0.0051,0.0297,0.2109</t>
   </si>
 </sst>
 </file>
@@ -1965,7 +1974,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1979,7 +1988,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1993,7 +2002,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2007,7 +2016,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2021,7 +2030,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2035,7 +2044,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2049,7 +2058,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2063,7 +2072,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2077,7 +2086,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2091,7 +2100,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2105,7 +2114,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2119,7 +2128,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2133,7 +2142,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2147,7 +2156,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2161,7 +2170,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2175,7 +2184,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,10 +2195,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,10 +2209,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,10 +2223,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2228,10 +2237,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,10 +2251,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,10 +2265,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2273,7 +2282,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2287,7 +2296,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2301,7 +2310,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2315,7 +2324,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2329,7 +2338,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2343,7 +2352,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2357,7 +2366,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2371,7 +2380,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2385,7 +2394,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2399,7 +2408,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2413,7 +2422,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2427,7 +2436,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2441,7 +2450,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2452,10 +2461,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,10 +2475,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2480,10 +2489,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2497,7 +2506,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2511,7 +2520,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2525,7 +2534,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2539,7 +2548,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,10 +2559,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2567,7 +2576,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2578,10 +2587,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,10 +2601,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,10 +2615,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,10 +2629,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2637,7 +2646,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2651,7 +2660,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2665,7 +2674,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2679,7 +2688,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2693,7 +2702,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2707,7 +2716,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2721,7 +2730,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2735,7 +2744,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2749,7 +2758,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2763,7 +2772,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2777,7 +2786,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2791,7 +2800,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2805,7 +2814,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,10 +2825,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2833,7 +2842,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2847,7 +2856,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,10 +2867,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2875,7 +2884,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,10 +2895,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,10 +2909,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2917,7 +2926,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2931,7 +2940,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2945,7 +2954,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2956,10 +2965,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2970,10 +2979,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2984,10 +2993,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,10 +3007,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3015,7 +3024,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3029,7 +3038,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3043,7 +3052,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3057,7 +3066,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3071,7 +3080,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3085,7 +3094,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3096,10 +3105,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,10 +3119,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3124,10 +3133,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3138,10 +3147,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3152,10 +3161,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3166,10 +3175,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3183,7 +3192,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3197,7 +3206,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3211,7 +3220,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3225,7 +3234,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3239,7 +3248,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3253,7 +3262,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3267,7 +3276,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3281,7 +3290,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3295,7 +3304,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3309,7 +3318,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3323,7 +3332,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3337,7 +3346,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3351,7 +3360,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3365,7 +3374,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3379,7 +3388,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3393,7 +3402,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3407,7 +3416,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3421,7 +3430,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3435,7 +3444,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3449,7 +3458,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,10 +3469,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,10 +3483,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,10 +3497,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,10 +3511,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,10 +3525,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,10 +3539,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3544,10 +3553,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3561,7 +3570,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3575,7 +3584,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3589,7 +3598,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3603,7 +3612,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3614,10 +3623,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,10 +3637,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,10 +3651,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,10 +3665,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,10 +3679,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,10 +3693,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3698,10 +3707,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3712,10 +3721,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3729,7 +3738,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3743,7 +3752,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3757,7 +3766,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3771,7 +3780,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3785,7 +3794,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3799,7 +3808,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3813,7 +3822,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3827,7 +3836,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3838,10 +3847,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3855,7 +3864,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3869,7 +3878,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3883,7 +3892,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3897,7 +3906,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,10 +3917,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3925,7 +3934,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3939,7 +3948,7 @@
         <v>266</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3953,7 +3962,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3967,7 +3976,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3981,7 +3990,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3995,7 +4004,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4006,10 +4015,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4023,7 +4032,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4034,10 +4043,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4051,7 +4060,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,10 +4071,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4079,7 +4088,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4093,7 +4102,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4107,7 +4116,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4121,7 +4130,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4135,7 +4144,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4149,7 +4158,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4163,7 +4172,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4177,7 +4186,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4191,7 +4200,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4202,10 +4211,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4219,7 +4228,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4233,7 +4242,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4247,7 +4256,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4261,7 +4270,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4275,7 +4284,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4289,7 +4298,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4303,7 +4312,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4317,7 +4326,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4331,7 +4340,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4345,7 +4354,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4359,7 +4368,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4370,10 +4379,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4387,7 +4396,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4401,7 +4410,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4415,7 +4424,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4429,7 +4438,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4443,7 +4452,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4457,7 +4466,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4471,7 +4480,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4485,7 +4494,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4499,7 +4508,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4513,7 +4522,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4527,7 +4536,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4541,7 +4550,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4555,7 +4564,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4569,7 +4578,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4583,7 +4592,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4597,7 +4606,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4611,7 +4620,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4622,10 +4631,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4639,7 +4648,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4653,7 +4662,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4667,7 +4676,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4681,7 +4690,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,10 +4701,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4706,10 +4715,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,10 +4729,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,10 +4743,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4751,7 +4760,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4762,10 +4771,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,10 +4785,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4793,7 +4802,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4807,7 +4816,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4821,7 +4830,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4835,7 +4844,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4849,7 +4858,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4863,7 +4872,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4877,7 +4886,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4891,7 +4900,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4905,7 +4914,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4919,7 +4928,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4933,7 +4942,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4947,7 +4956,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4961,7 +4970,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4975,7 +4984,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4989,7 +4998,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5003,7 +5012,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5017,7 +5026,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5031,7 +5040,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5045,7 +5054,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5059,7 +5068,7 @@
         <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5073,7 +5082,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5087,7 +5096,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5101,7 +5110,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5115,7 +5124,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5129,7 +5138,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5143,7 +5152,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5157,7 +5166,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5171,7 +5180,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5185,7 +5194,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5199,7 +5208,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5213,7 +5222,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5227,7 +5236,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5241,7 +5250,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5255,7 +5264,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5269,7 +5278,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5283,7 +5292,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5297,7 +5306,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5311,7 +5320,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5325,7 +5334,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5339,7 +5348,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5353,7 +5362,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5367,7 +5376,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5381,7 +5390,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5395,7 +5404,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5409,7 +5418,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5423,7 +5432,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5437,7 +5446,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5451,7 +5460,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5465,7 +5474,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5479,7 +5488,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5493,7 +5502,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5507,7 +5516,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5521,7 +5530,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
